--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_los_rios.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_los_rios.xlsx
@@ -404,7 +404,7 @@
         <v>24.26057622985109</v>
       </c>
       <c r="D2">
-        <v>1.723518492951049</v>
+        <v>2.962061692591616</v>
       </c>
       <c r="E2">
         <v>21.36444028883957</v>
@@ -429,7 +429,7 @@
         <v>29.92819843342037</v>
       </c>
       <c r="D3">
-        <v>1.273482959268496</v>
+        <v>2.057756883814641</v>
       </c>
       <c r="E3">
         <v>27.22120658135283</v>
@@ -454,7 +454,7 @@
         <v>27.45421547599406</v>
       </c>
       <c r="D4">
-        <v>1.519047619047619</v>
+        <v>2.605760963026655</v>
       </c>
       <c r="E4">
         <v>23.14197592279375</v>
@@ -479,7 +479,7 @@
         <v>27.89973091630081</v>
       </c>
       <c r="D5">
-        <v>1.519638437533628</v>
+        <v>2.638146833551279</v>
       </c>
       <c r="E5">
         <v>22.86141362374546</v>
@@ -504,7 +504,7 @@
         <v>28.57984678845021</v>
       </c>
       <c r="D6">
-        <v>1.476508120649652</v>
+        <v>2.554440541896638</v>
       </c>
       <c r="E6">
         <v>23.33996955146973</v>
@@ -529,7 +529,7 @@
         <v>29.94933383373992</v>
       </c>
       <c r="D7">
-        <v>1.572904368358914</v>
+        <v>2.973772321428572</v>
       </c>
       <c r="E7">
         <v>20.55753126075484</v>
@@ -554,7 +554,7 @@
         <v>27.4442538593482</v>
       </c>
       <c r="D8">
-        <v>1.480948348856901</v>
+        <v>2.495007132667618</v>
       </c>
       <c r="E8">
         <v>23.92491467576792</v>
@@ -579,7 +579,7 @@
         <v>28.14029987760098</v>
       </c>
       <c r="D9">
-        <v>1.567292128769259</v>
+        <v>2.803946803946804</v>
       </c>
       <c r="E9">
         <v>21.7723292469352</v>
@@ -604,7 +604,7 @@
         <v>26.80015552099533</v>
       </c>
       <c r="D10">
-        <v>1.512051734273956</v>
+        <v>2.542255609370367</v>
       </c>
       <c r="E10">
         <v>23.67657383571262</v>
@@ -629,7 +629,7 @@
         <v>30.13735523835174</v>
       </c>
       <c r="D11">
-        <v>1.532397853900124</v>
+        <v>2.84739263803681</v>
       </c>
       <c r="E11">
         <v>21.25162972620599</v>
@@ -654,7 +654,7 @@
         <v>27.09728239464356</v>
       </c>
       <c r="D12">
-        <v>1.506526898734177</v>
+        <v>2.545788770053476</v>
       </c>
       <c r="E12">
         <v>23.60924800757516</v>
@@ -679,7 +679,7 @@
         <v>34.15933589394128</v>
       </c>
       <c r="D13">
-        <v>1.757239277160897</v>
+        <v>4.395969498910675</v>
       </c>
       <c r="E13">
         <v>14.49778900821225</v>

--- a/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_los_rios.xlsx
+++ b/output/graficos_otras_relaciones/plot_comunal_d_otrasrel_a_2024_los_rios.xlsx
@@ -398,22 +398,22 @@
         </is>
       </c>
       <c r="B2">
+        <v>24.26057622985109</v>
+      </c>
+      <c r="C2">
         <v>33.76026915648281</v>
-      </c>
-      <c r="C2">
-        <v>24.26057622985109</v>
       </c>
       <c r="D2">
         <v>2.962061692591616</v>
       </c>
       <c r="E2">
-        <v>21.36444028883957</v>
+        <v>15.35276954792776</v>
       </c>
       <c r="F2">
         <v>63.28279016323265</v>
       </c>
       <c r="G2">
-        <v>15.35276954792776</v>
+        <v>21.36444028883957</v>
       </c>
     </row>
     <row r="3">
@@ -423,22 +423,22 @@
         </is>
       </c>
       <c r="B3">
+        <v>29.92819843342037</v>
+      </c>
+      <c r="C3">
         <v>48.59660574412533</v>
-      </c>
-      <c r="C3">
-        <v>29.92819843342037</v>
       </c>
       <c r="D3">
         <v>2.057756883814641</v>
       </c>
       <c r="E3">
-        <v>27.22120658135283</v>
+        <v>16.76416819012797</v>
       </c>
       <c r="F3">
         <v>56.01462522851919</v>
       </c>
       <c r="G3">
-        <v>16.76416819012797</v>
+        <v>27.22120658135283</v>
       </c>
     </row>
     <row r="4">
@@ -448,22 +448,22 @@
         </is>
       </c>
       <c r="B4">
+        <v>27.45421547599406</v>
+      </c>
+      <c r="C4">
         <v>38.37650552714074</v>
-      </c>
-      <c r="C4">
-        <v>27.45421547599406</v>
       </c>
       <c r="D4">
         <v>2.605760963026655</v>
       </c>
       <c r="E4">
+        <v>16.55556661028753</v>
+      </c>
+      <c r="F4">
+        <v>60.30245746691872</v>
+      </c>
+      <c r="G4">
         <v>23.14197592279375</v>
-      </c>
-      <c r="F4">
-        <v>60.30245746691871</v>
-      </c>
-      <c r="G4">
-        <v>16.55556661028753</v>
       </c>
     </row>
     <row r="5">
@@ -473,22 +473,22 @@
         </is>
       </c>
       <c r="B5">
+        <v>27.89973091630081</v>
+      </c>
+      <c r="C5">
         <v>37.90539583628381</v>
-      </c>
-      <c r="C5">
-        <v>27.89973091630081</v>
       </c>
       <c r="D5">
         <v>2.638146833551279</v>
       </c>
       <c r="E5">
-        <v>22.86141362374546</v>
+        <v>16.82682041426436</v>
       </c>
       <c r="F5">
         <v>60.31176596199018</v>
       </c>
       <c r="G5">
-        <v>16.82682041426436</v>
+        <v>22.86141362374546</v>
       </c>
     </row>
     <row r="6">
@@ -498,22 +498,22 @@
         </is>
       </c>
       <c r="B6">
+        <v>28.57984678845021</v>
+      </c>
+      <c r="C6">
         <v>39.14751522294245</v>
-      </c>
-      <c r="C6">
-        <v>28.57984678845021</v>
       </c>
       <c r="D6">
         <v>2.554440541896638</v>
       </c>
       <c r="E6">
-        <v>23.33996955146973</v>
+        <v>17.03946597962291</v>
       </c>
       <c r="F6">
         <v>59.62056446890737</v>
       </c>
       <c r="G6">
-        <v>17.03946597962291</v>
+        <v>23.33996955146973</v>
       </c>
     </row>
     <row r="7">
@@ -523,22 +523,22 @@
         </is>
       </c>
       <c r="B7">
+        <v>29.94933383373992</v>
+      </c>
+      <c r="C7">
         <v>33.62732219928692</v>
-      </c>
-      <c r="C7">
-        <v>29.94933383373992</v>
       </c>
       <c r="D7">
         <v>2.973772321428572</v>
       </c>
       <c r="E7">
-        <v>20.55753126075484</v>
+        <v>18.30905127910979</v>
       </c>
       <c r="F7">
         <v>61.13341746013537</v>
       </c>
       <c r="G7">
-        <v>18.30905127910979</v>
+        <v>20.55753126075484</v>
       </c>
     </row>
     <row r="8">
@@ -548,22 +548,22 @@
         </is>
       </c>
       <c r="B8">
+        <v>27.4442538593482</v>
+      </c>
+      <c r="C8">
         <v>40.0800457404231</v>
-      </c>
-      <c r="C8">
-        <v>27.4442538593482</v>
       </c>
       <c r="D8">
         <v>2.495007132667618</v>
       </c>
       <c r="E8">
-        <v>23.92491467576792</v>
+        <v>16.38225255972696</v>
       </c>
       <c r="F8">
         <v>59.69283276450512</v>
       </c>
       <c r="G8">
-        <v>16.38225255972696</v>
+        <v>23.92491467576792</v>
       </c>
     </row>
     <row r="9">
@@ -573,22 +573,22 @@
         </is>
       </c>
       <c r="B9">
+        <v>28.14029987760098</v>
+      </c>
+      <c r="C9">
         <v>35.66401468788249</v>
-      </c>
-      <c r="C9">
-        <v>28.14029987760098</v>
       </c>
       <c r="D9">
         <v>2.803946803946804</v>
       </c>
       <c r="E9">
-        <v>21.7723292469352</v>
+        <v>17.17921774664332</v>
       </c>
       <c r="F9">
         <v>61.04845300642149</v>
       </c>
       <c r="G9">
-        <v>17.17921774664332</v>
+        <v>21.7723292469352</v>
       </c>
     </row>
     <row r="10">
@@ -598,22 +598,22 @@
         </is>
       </c>
       <c r="B10">
+        <v>26.80015552099533</v>
+      </c>
+      <c r="C10">
         <v>39.33514774494557</v>
-      </c>
-      <c r="C10">
-        <v>26.80015552099533</v>
       </c>
       <c r="D10">
         <v>2.542255609370367</v>
       </c>
       <c r="E10">
-        <v>23.67657383571262</v>
+        <v>16.13152351977533</v>
       </c>
       <c r="F10">
         <v>60.19190264451205</v>
       </c>
       <c r="G10">
-        <v>16.13152351977533</v>
+        <v>23.67657383571262</v>
       </c>
     </row>
     <row r="11">
@@ -623,22 +623,22 @@
         </is>
       </c>
       <c r="B11">
+        <v>30.13735523835174</v>
+      </c>
+      <c r="C11">
         <v>35.11984917856181</v>
-      </c>
-      <c r="C11">
-        <v>30.13735523835174</v>
       </c>
       <c r="D11">
         <v>2.84739263803681</v>
       </c>
       <c r="E11">
-        <v>21.25162972620599</v>
+        <v>18.23663624511082</v>
       </c>
       <c r="F11">
         <v>60.51173402868317</v>
       </c>
       <c r="G11">
-        <v>18.23663624511082</v>
+        <v>21.25162972620599</v>
       </c>
     </row>
     <row r="12">
@@ -648,22 +648,22 @@
         </is>
       </c>
       <c r="B12">
+        <v>27.09728239464356</v>
+      </c>
+      <c r="C12">
         <v>39.28055664959958</v>
-      </c>
-      <c r="C12">
-        <v>27.09728239464356</v>
       </c>
       <c r="D12">
         <v>2.545788770053476</v>
       </c>
       <c r="E12">
-        <v>23.60924800757516</v>
+        <v>16.2865935453326</v>
       </c>
       <c r="F12">
         <v>60.10415844709224</v>
       </c>
       <c r="G12">
-        <v>16.2865935453326</v>
+        <v>23.60924800757516</v>
       </c>
     </row>
     <row r="13">
@@ -673,22 +673,22 @@
         </is>
       </c>
       <c r="B13">
+        <v>34.15933589394128</v>
+      </c>
+      <c r="C13">
         <v>22.74811051914261</v>
-      </c>
-      <c r="C13">
-        <v>34.15933589394128</v>
       </c>
       <c r="D13">
         <v>4.395969498910675</v>
       </c>
       <c r="E13">
-        <v>14.49778900821225</v>
+        <v>21.77037271004422</v>
       </c>
       <c r="F13">
-        <v>63.73183828174351</v>
+        <v>63.73183828174353</v>
       </c>
       <c r="G13">
-        <v>21.77037271004422</v>
+        <v>14.49778900821226</v>
       </c>
     </row>
   </sheetData>
